--- a/samples/check_back_template_v1.xlsx
+++ b/samples/check_back_template_v1.xlsx
@@ -460,259 +460,264 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AX2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="75" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>Opportunity Name</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Opportunity (linked)</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>SL2</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>TCV $</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Closed on (MM/YY)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Competitor</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Migrating from</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Migrating to</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Partner</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>CSM Engagement Model (linked)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>CSM name</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Sub #</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Sub Term</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Sub start date (MM/DD/YYYY)</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Add-ons included or not</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Calling Setup Assist included (Y/N)</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Provisioned/Entitled Lic Calling</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Active Lic Calling</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Customer org id</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Notes from Calling Analytics</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Notes from provisioned features</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>CCEP trial (Y/N)</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>(G/Y/R)</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>TAC/BEMS</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>AAR $</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Collab AE/SE</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Service lines</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>Sub term (months)</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>Subscription dates</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>Platforms</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>Trend active users 90d</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>Trend call volume 90d</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>Lic Professional (used/entitled)</t>
         </is>
       </c>
-      <c r="AH1" s="4" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>Lic Standard (used/entitled)</t>
         </is>
       </c>
-      <c r="AI1" s="4" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>Lic Workspace (used/entitled)</t>
         </is>
       </c>
-      <c r="AJ1" s="4" t="inlineStr">
+      <c r="AK1" s="4" t="inlineStr">
         <is>
           <t>Active % of provisioned</t>
         </is>
       </c>
-      <c r="AK1" s="4" t="inlineStr">
+      <c r="AL1" s="4" t="inlineStr">
         <is>
           <t>External calls</t>
         </is>
       </c>
-      <c r="AL1" s="4" t="inlineStr">
+      <c r="AM1" s="4" t="inlineStr">
         <is>
           <t>Meetings usage</t>
         </is>
       </c>
-      <c r="AM1" s="4" t="inlineStr">
+      <c r="AN1" s="4" t="inlineStr">
         <is>
           <t>Messaging usage</t>
         </is>
       </c>
-      <c r="AN1" s="4" t="inlineStr">
+      <c r="AO1" s="4" t="inlineStr">
         <is>
           <t>Auto Attendant count</t>
         </is>
       </c>
-      <c r="AO1" s="4" t="inlineStr">
+      <c r="AP1" s="4" t="inlineStr">
         <is>
           <t>Hunt Groups count</t>
         </is>
       </c>
-      <c r="AP1" s="4" t="inlineStr">
+      <c r="AQ1" s="4" t="inlineStr">
         <is>
           <t>Call Queues count</t>
         </is>
       </c>
-      <c r="AQ1" s="4" t="inlineStr">
+      <c r="AR1" s="4" t="inlineStr">
         <is>
           <t>Connected-UC (Y/N)</t>
         </is>
       </c>
-      <c r="AR1" s="4" t="inlineStr">
+      <c r="AS1" s="4" t="inlineStr">
         <is>
           <t>Virtual Lines count</t>
         </is>
       </c>
-      <c r="AS1" s="4" t="inlineStr">
+      <c r="AT1" s="4" t="inlineStr">
         <is>
           <t>Data gathered by</t>
         </is>
       </c>
-      <c r="AT1" s="4" t="inlineStr">
+      <c r="AU1" s="4" t="inlineStr">
         <is>
           <t>Data gathered date</t>
         </is>
       </c>
-      <c r="AU1" s="4" t="inlineStr">
+      <c r="AV1" s="4" t="inlineStr">
         <is>
           <t>Salesforce URL</t>
         </is>
       </c>
-      <c r="AV1" s="4" t="inlineStr">
+      <c r="AW1" s="4" t="inlineStr">
         <is>
           <t>Success Portal</t>
         </is>
       </c>
-      <c r="AW1" s="4" t="inlineStr">
+      <c r="AX1" s="4" t="inlineStr">
         <is>
           <t>Recommended Actions</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="M2" s="1" t="n"/>
-      <c r="Q2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/check_back_template_v1.xlsx
+++ b/samples/check_back_template_v1.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="75" customHeight="1">
@@ -681,35 +681,40 @@
       </c>
       <c r="AR1" s="4" t="inlineStr">
         <is>
+          <t>Customer Assist Queues count</t>
+        </is>
+      </c>
+      <c r="AS1" s="4" t="inlineStr">
+        <is>
           <t>Connected-UC (Y/N)</t>
         </is>
       </c>
-      <c r="AS1" s="4" t="inlineStr">
+      <c r="AT1" s="4" t="inlineStr">
         <is>
           <t>Virtual Lines count</t>
         </is>
       </c>
-      <c r="AT1" s="4" t="inlineStr">
+      <c r="AU1" s="4" t="inlineStr">
         <is>
           <t>Data gathered by</t>
         </is>
       </c>
-      <c r="AU1" s="4" t="inlineStr">
+      <c r="AV1" s="4" t="inlineStr">
         <is>
           <t>Data gathered date</t>
         </is>
       </c>
-      <c r="AV1" s="4" t="inlineStr">
+      <c r="AW1" s="4" t="inlineStr">
         <is>
           <t>Salesforce URL</t>
         </is>
       </c>
-      <c r="AW1" s="4" t="inlineStr">
+      <c r="AX1" s="4" t="inlineStr">
         <is>
           <t>Success Portal</t>
         </is>
       </c>
-      <c r="AX1" s="4" t="inlineStr">
+      <c r="AY1" s="4" t="inlineStr">
         <is>
           <t>Recommended Actions</t>
         </is>

--- a/samples/check_back_template_v1.xlsx
+++ b/samples/check_back_template_v1.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Customer Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -581,7 +581,7 @@
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
-          <t>(G/Y/R)</t>
+          <t>(G/Y/R/U)</t>
         </is>
       </c>
       <c r="Y1" s="4" t="inlineStr">
